--- a/elee201_hw_answers.xlsx
+++ b/elee201_hw_answers.xlsx
@@ -5,16 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grovecitycollege-my.sharepoint.com/personal/rumbaughlk_gcc_edu/Documents/Documents/Teaching/Linear Circuits/Homework/Autograding/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grovecitycollege-my.sharepoint.com/personal/rumbaughlk_gcc_edu/Documents/Documents/Teaching/Linear Circuits/Homework/HW Checker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="67" documentId="8_{4FFE368D-BB14-4855-8871-B45586B98510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0F00318-C274-4B33-B858-FE5905CE8ACA}"/>
+  <xr:revisionPtr revIDLastSave="217" documentId="8_{4FFE368D-BB14-4855-8871-B45586B98510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A2F6AF0-E262-4213-9E2F-254A391E2B8F}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{016CC8A0-D84E-482E-B6C9-E87D3311BA45}"/>
+    <workbookView xWindow="-27090" yWindow="1710" windowWidth="21600" windowHeight="11055" activeTab="1" xr2:uid="{016CC8A0-D84E-482E-B6C9-E87D3311BA45}"/>
   </bookViews>
   <sheets>
-    <sheet name="HW5" sheetId="1" r:id="rId1"/>
-    <sheet name="HW6" sheetId="2" r:id="rId2"/>
+    <sheet name="HW3" sheetId="3" r:id="rId1"/>
+    <sheet name="HW4" sheetId="4" r:id="rId2"/>
+    <sheet name="HW5" sheetId="1" r:id="rId3"/>
+    <sheet name="HW6" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="48">
   <si>
     <t>Problem</t>
   </si>
@@ -115,6 +117,75 @@
   </si>
   <si>
     <t>2.58</t>
+  </si>
+  <si>
+    <t>ne</t>
+  </si>
+  <si>
+    <t>x10^18 electrons</t>
+  </si>
+  <si>
+    <t>mC</t>
+  </si>
+  <si>
+    <t>q(t) max</t>
+  </si>
+  <si>
+    <t>mA</t>
+  </si>
+  <si>
+    <t>i(t) max</t>
+  </si>
+  <si>
+    <t>i(t) final</t>
+  </si>
+  <si>
+    <t>q(t=5)</t>
+  </si>
+  <si>
+    <t>q(t) final asymptote</t>
+  </si>
+  <si>
+    <t>i(t=1)</t>
+  </si>
+  <si>
+    <t>i(t=3)</t>
+  </si>
+  <si>
+    <t>i(t=6)</t>
+  </si>
+  <si>
+    <t>IY</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>Tmax</t>
+  </si>
+  <si>
+    <t>deg C</t>
+  </si>
+  <si>
+    <t>R0</t>
+  </si>
+  <si>
+    <t>R1800</t>
+  </si>
+  <si>
+    <t>R20</t>
+  </si>
+  <si>
+    <t>I1800</t>
+  </si>
+  <si>
+    <t>I20</t>
+  </si>
+  <si>
+    <t>2.6ab</t>
+  </si>
+  <si>
+    <t>2.6cd</t>
   </si>
 </sst>
 </file>
@@ -395,6 +466,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -407,11 +483,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -745,6 +816,521 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25AE21B6-565E-4D2D-AF85-3C3B920C40A1}">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="5" max="5" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A1" s="10"/>
+      <c r="B1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="24"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="12">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="1">
+        <v>6.25</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="15"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="6"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="12">
+        <v>1.18</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="1">
+        <v>50</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="6">
+        <v>2</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="1">
+        <v>-1</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="6"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="6"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="12">
+        <v>1.21</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="1">
+        <v>30</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="6">
+        <v>1</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="1">
+        <v>75</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" s="6">
+        <v>1</v>
+      </c>
+      <c r="J5" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="K5" s="1">
+        <v>125</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M5" s="6"/>
+    </row>
+    <row r="6" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="13">
+        <v>1.22</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="8">
+        <v>2</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="8">
+        <v>0</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="J6" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="K6" s="8">
+        <v>-2</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M6" s="9">
+        <v>0.25</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="J1:M1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4B576BD-563F-4598-AF96-EAE1A8A5DD05}">
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="5" max="5" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A1" s="10"/>
+      <c r="B1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="24"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="1">
+        <v>125</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="6">
+        <v>10</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G3" s="1">
+        <v>11.9</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="J3" s="15"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="6"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="1">
+        <v>8.43</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="J4" s="15"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="6"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="12">
+        <v>2.7</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="1">
+        <v>47</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5" s="6">
+        <v>1</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="G5" s="1">
+        <v>55.6</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" s="6">
+        <v>1</v>
+      </c>
+      <c r="J5" s="15"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="6"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A6" s="12">
+        <v>2.8</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="1">
+        <v>6.41</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G6" s="1">
+        <v>17.2</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="J6" s="15"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="6"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A7" s="12">
+        <v>2.11</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2500</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="6">
+        <v>100</v>
+      </c>
+      <c r="F7" s="5"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="15"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="6"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A8" s="12">
+        <v>2.15</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="F8" s="5"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="6"/>
+    </row>
+    <row r="9" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="13">
+        <v>2.19</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="8">
+        <v>3.57</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" s="8">
+        <v>2.86</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="J9" s="16"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="9"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="J1:M1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7749778-6856-40A2-9432-9BE41E2A7C62}">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -756,24 +1342,24 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="10"/>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="17" t="s">
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="20" t="s">
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="19"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="24"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
@@ -950,7 +1536,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4D3BB39-110F-4C3C-ACE5-9DDB4799F102}">
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -962,24 +1548,24 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="10"/>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="20" t="s">
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="20" t="s">
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="19"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="24"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
@@ -1023,7 +1609,7 @@
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" s="22">
+      <c r="A3" s="18">
         <v>2.29</v>
       </c>
       <c r="B3" s="5" t="s">
@@ -1048,7 +1634,7 @@
       <c r="M3" s="6"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" s="22">
+      <c r="A4" s="18">
         <v>2.36</v>
       </c>
       <c r="B4" s="5" t="s">
@@ -1073,7 +1659,7 @@
       <c r="M4" s="6"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" s="23" t="s">
+      <c r="A5" s="19" t="s">
         <v>21</v>
       </c>
       <c r="B5" s="5" t="s">
@@ -1082,7 +1668,7 @@
       <c r="C5" s="1">
         <v>5</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="D5" s="17" t="s">
         <v>20</v>
       </c>
       <c r="E5" s="6">
@@ -1106,7 +1692,7 @@
       <c r="M5" s="6"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="18" t="s">
         <v>22</v>
       </c>
       <c r="B6" s="5" t="s">
@@ -1115,7 +1701,7 @@
       <c r="C6" s="1">
         <v>1.97</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="D6" s="17" t="s">
         <v>11</v>
       </c>
       <c r="E6" s="6">
@@ -1131,7 +1717,7 @@
       <c r="M6" s="6"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="18" t="s">
         <v>23</v>
       </c>
       <c r="B7" s="5" t="s">
@@ -1140,7 +1726,7 @@
       <c r="C7" s="1">
         <v>10</v>
       </c>
-      <c r="D7" s="21" t="s">
+      <c r="D7" s="17" t="s">
         <v>20</v>
       </c>
       <c r="E7" s="6">
@@ -1156,7 +1742,7 @@
       <c r="M7" s="6"/>
     </row>
     <row r="8" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="20" t="s">
         <v>24</v>
       </c>
       <c r="B8" s="7" t="s">
@@ -1165,7 +1751,7 @@
       <c r="C8" s="8">
         <v>3.99</v>
       </c>
-      <c r="D8" s="25" t="s">
+      <c r="D8" s="21" t="s">
         <v>15</v>
       </c>
       <c r="E8" s="9">

--- a/elee201_hw_answers.xlsx
+++ b/elee201_hw_answers.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grovecitycollege-my.sharepoint.com/personal/rumbaughlk_gcc_edu/Documents/Documents/Teaching/Linear Circuits/Homework/HW Checker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="217" documentId="8_{4FFE368D-BB14-4855-8871-B45586B98510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A2F6AF0-E262-4213-9E2F-254A391E2B8F}"/>
+  <xr:revisionPtr revIDLastSave="346" documentId="8_{4FFE368D-BB14-4855-8871-B45586B98510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F19E087-DC1B-42B2-B7AF-F964A98A24F2}"/>
   <bookViews>
-    <workbookView xWindow="-27090" yWindow="1710" windowWidth="21600" windowHeight="11055" activeTab="1" xr2:uid="{016CC8A0-D84E-482E-B6C9-E87D3311BA45}"/>
+    <workbookView xWindow="-21900" yWindow="1770" windowWidth="21600" windowHeight="11055" activeTab="5" xr2:uid="{016CC8A0-D84E-482E-B6C9-E87D3311BA45}"/>
   </bookViews>
   <sheets>
     <sheet name="HW3" sheetId="3" r:id="rId1"/>
     <sheet name="HW4" sheetId="4" r:id="rId2"/>
     <sheet name="HW5" sheetId="1" r:id="rId3"/>
     <sheet name="HW6" sheetId="2" r:id="rId4"/>
+    <sheet name="HW7" sheetId="5" r:id="rId5"/>
+    <sheet name="HW8" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="67">
   <si>
     <t>Problem</t>
   </si>
@@ -182,10 +184,67 @@
     <t>I20</t>
   </si>
   <si>
-    <t>2.6ab</t>
-  </si>
-  <si>
-    <t>2.6cd</t>
+    <t>3.27</t>
+  </si>
+  <si>
+    <t>I2</t>
+  </si>
+  <si>
+    <t>I3</t>
+  </si>
+  <si>
+    <t>3.33</t>
+  </si>
+  <si>
+    <t>I1</t>
+  </si>
+  <si>
+    <t>3.37</t>
+  </si>
+  <si>
+    <t>I4</t>
+  </si>
+  <si>
+    <t>3.57</t>
+  </si>
+  <si>
+    <t>VOUT</t>
+  </si>
+  <si>
+    <t>3.66</t>
+  </si>
+  <si>
+    <t>VTH</t>
+  </si>
+  <si>
+    <t>RTH</t>
+  </si>
+  <si>
+    <t>RL</t>
+  </si>
+  <si>
+    <t>3.63</t>
+  </si>
+  <si>
+    <t>VX'</t>
+  </si>
+  <si>
+    <t>VX''</t>
+  </si>
+  <si>
+    <t>VX'''</t>
+  </si>
+  <si>
+    <t>3.71</t>
+  </si>
+  <si>
+    <t>Answer 4</t>
+  </si>
+  <si>
+    <t>Answer 5</t>
+  </si>
+  <si>
+    <t>ISC</t>
   </si>
 </sst>
 </file>
@@ -448,7 +507,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -483,6 +542,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1035,7 +1095,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4B576BD-563F-4598-AF96-EAE1A8A5DD05}">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="5" max="5" width="9.36328125" bestFit="1" customWidth="1"/>
@@ -1043,7 +1103,7 @@
     <col min="13" max="13" width="9.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" s="10"/>
       <c r="B1" s="22" t="s">
         <v>1</v>
@@ -1063,8 +1123,14 @@
       <c r="K1" s="23"/>
       <c r="L1" s="23"/>
       <c r="M1" s="24"/>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N1" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="O1" s="23"/>
+      <c r="P1" s="23"/>
+      <c r="Q1" s="24"/>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
         <v>0</v>
       </c>
@@ -1104,10 +1170,22 @@
       <c r="M2" s="4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" s="12" t="s">
-        <v>46</v>
+      <c r="N2" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A3" s="12">
+        <v>2.6</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>42</v>
@@ -1133,125 +1211,149 @@
       <c r="I3" s="6">
         <v>0.5</v>
       </c>
-      <c r="J3" s="15"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="6"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" s="12" t="s">
+      <c r="J3" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="K3" s="1">
+        <v>8.43</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M3" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="O3" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q3" s="6">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A4" s="12">
+        <v>2.7</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="1">
         <v>47</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C4" s="1">
-        <v>8.43</v>
-      </c>
       <c r="D4" s="1" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="E4" s="6">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G4" s="1">
-        <v>0.8</v>
+        <v>55.6</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="I4" s="6">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="J4" s="15"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="6"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N4" s="15"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="6"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5" s="12">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C5" s="1">
-        <v>47</v>
+        <v>6.41</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E5" s="6">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="G5" s="1">
-        <v>55.6</v>
+        <v>17.2</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="I5" s="6">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J5" s="15"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="6"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N5" s="15"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="6"/>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
-        <v>2.8</v>
+        <v>2.11</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>38</v>
       </c>
       <c r="C6" s="1">
-        <v>6.41</v>
+        <v>2500</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E6" s="6">
-        <v>0.25</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="G6" s="1">
-        <v>17.2</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I6" s="6">
-        <v>0.5</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F6" s="5"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="6"/>
       <c r="J6" s="15"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="6"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N6" s="15"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="6"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7" s="12">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="C7" s="1">
-        <v>2500</v>
+        <v>2.4300000000000002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E7" s="6">
-        <v>100</v>
+        <v>0.1</v>
       </c>
       <c r="F7" s="5"/>
       <c r="G7" s="1"/>
@@ -1261,70 +1363,54 @@
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="6"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A8" s="12">
-        <v>2.15</v>
-      </c>
-      <c r="B8" s="5" t="s">
+      <c r="N7" s="15"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="6"/>
+    </row>
+    <row r="8" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="13">
+        <v>2.19</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="1">
-        <v>2.4300000000000002</v>
-      </c>
-      <c r="D8" s="1" t="s">
+      <c r="C8" s="8">
+        <v>3.57</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="9">
         <v>0.1</v>
       </c>
-      <c r="F8" s="5"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="6"/>
-    </row>
-    <row r="9" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="13">
-        <v>2.19</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="8">
-        <v>3.57</v>
-      </c>
-      <c r="D9" s="8" t="s">
+      <c r="F8" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="8">
+        <v>2.86</v>
+      </c>
+      <c r="H8" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="9">
+      <c r="I8" s="9">
         <v>0.1</v>
       </c>
-      <c r="F9" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G9" s="8">
-        <v>2.86</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="I9" s="9">
-        <v>0.1</v>
-      </c>
-      <c r="J9" s="16"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="9"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="16"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="9"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="F1:I1"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:Q1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1775,4 +1861,578 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD234E7E-2C06-43FB-B347-39C61E37A90D}">
+  <dimension ref="A1:Y6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="5" max="5" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A1" s="10"/>
+      <c r="B1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="O1" s="23"/>
+      <c r="P1" s="23"/>
+      <c r="Q1" s="24"/>
+      <c r="R1" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="S1" s="23"/>
+      <c r="T1" s="23"/>
+      <c r="U1" s="24"/>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="N2" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="R2" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A3" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="1">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="G3" s="1">
+        <v>-3</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="K3" s="1">
+        <v>-120</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M3" s="6">
+        <v>1</v>
+      </c>
+      <c r="N3" s="15"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="15"/>
+      <c r="S3" s="1"/>
+      <c r="T3" s="1"/>
+      <c r="U3" s="6"/>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A4" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="G4" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="J4" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="K4" s="1">
+        <v>-3</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M4" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="N4" s="15"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="15"/>
+      <c r="S4" s="1"/>
+      <c r="T4" s="1"/>
+      <c r="U4" s="6"/>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A5" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2.15</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="J5" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="K5" s="1">
+        <v>2.9</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M5" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="O5" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="P5" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q5" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="R5" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="S5" s="1">
+        <v>0.85</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U5" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="V5" s="15"/>
+      <c r="W5" s="1"/>
+      <c r="X5" s="1"/>
+      <c r="Y5" s="6"/>
+    </row>
+    <row r="6" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="8">
+        <v>2</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="F6" s="16"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="16"/>
+      <c r="O6" s="8"/>
+      <c r="P6" s="8"/>
+      <c r="Q6" s="9"/>
+      <c r="R6" s="16"/>
+      <c r="S6" s="8"/>
+      <c r="T6" s="8"/>
+      <c r="U6" s="9"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:Q1"/>
+    <mergeCell ref="R1:U1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBF83AC0-F5C8-4688-9D0E-A686A165ABE2}">
+  <dimension ref="A1:Q5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="5" max="5" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A1" s="10"/>
+      <c r="B1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="O1" s="23"/>
+      <c r="P1" s="23"/>
+      <c r="Q1" s="24"/>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="N2" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A3" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="1">
+        <v>-4</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="G3" s="1">
+        <v>5</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="K3" s="1">
+        <v>3</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M3" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="N3" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="O3" s="1">
+        <v>3</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q3" s="6">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A4" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="G4" s="1">
+        <v>5</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="J4" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="K4" s="1">
+        <v>-15</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M4" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="N4" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="O4" s="1">
+        <v>-10</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q4" s="6">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" s="8">
+        <v>17.489999999999998</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="G5" s="8">
+        <v>3.86</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="J5" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="K5" s="8">
+        <v>4.53</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="M5" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="N5" s="16"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
+      <c r="Q5" s="9"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:Q1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" verticalDpi="0" r:id="rId1"/>
+</worksheet>
 </file>